--- a/Documentacion P2/WBS.xlsx
+++ b/Documentacion P2/WBS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\5to\BDII\Documentacion P1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\oficina\Documentacion P2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C13D7D6-6F8F-4240-88E6-16985847748B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241B927F-18FF-4BDF-A2B8-3A1701B7660C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="168" yWindow="1056" windowWidth="22872" windowHeight="11184" firstSheet="10" activeTab="15" xr2:uid="{9B569A39-F1BF-40FC-A0D0-8493B137E432}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="14" activeTab="15" xr2:uid="{9B569A39-F1BF-40FC-A0D0-8493B137E432}"/>
   </bookViews>
   <sheets>
     <sheet name="Consulta de requisitos" sheetId="1" r:id="rId1"/>
@@ -937,58 +937,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1030,11 +979,407 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="181">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1079,6 +1424,23 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1096,89 +1458,39 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1201,6 +1513,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1208,15 +1529,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1266,6 +1578,23 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1283,89 +1612,89 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF242424"/>
+        <name val="Aptos Narrow"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF242424"/>
+        <name val="Aptos Narrow"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1388,6 +1717,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1395,15 +1733,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1453,6 +1782,23 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1487,74 +1833,24 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -1576,6 +1872,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1583,15 +1888,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1658,6 +1954,23 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1675,123 +1988,38 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF242424"/>
-        <name val="Aptos Narrow"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF242424"/>
-        <name val="Aptos Narrow"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1814,6 +2042,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1821,15 +2058,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1873,7 +2101,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -1890,10 +2120,15 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -1907,58 +2142,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -1975,12 +2161,33 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1989,13 +2196,21 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2003,22 +2218,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2054,134 +2253,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -2190,6 +2261,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2197,15 +2277,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2249,125 +2320,129 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2375,19 +2450,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -2420,6 +2482,185 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -2428,6 +2669,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2435,15 +2685,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2615,6 +2856,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2622,15 +2872,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2748,22 +2989,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2781,22 +3006,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2814,22 +3023,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -2853,6 +3046,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2860,15 +3062,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -3040,6 +3233,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -3047,15 +3249,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -3099,7 +3292,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -3116,7 +3311,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -3133,27 +3330,15 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -3167,7 +3352,45 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -3175,40 +3398,6 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -3216,13 +3405,21 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -3230,22 +3427,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -3289,7 +3470,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -3306,7 +3489,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -3323,27 +3508,15 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -3357,44 +3530,51 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -3403,13 +3583,21 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -3417,22 +3605,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -3476,124 +3648,146 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3601,19 +3795,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -3654,124 +3835,112 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3779,19 +3948,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -3821,164 +3977,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -4730,118 +4728,118 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7868C214-BFDF-4A25-882F-CAE0EB840B88}" name="Tabla1" displayName="Tabla1" ref="A2:H3" totalsRowShown="0" headerRowDxfId="169" headerRowBorderDxfId="179" tableBorderDxfId="180" totalsRowBorderDxfId="178">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7868C214-BFDF-4A25-882F-CAE0EB840B88}" name="Tabla1" displayName="Tabla1" ref="A2:H3" totalsRowShown="0" headerRowDxfId="170" headerRowBorderDxfId="169" tableBorderDxfId="168" totalsRowBorderDxfId="167">
   <autoFilter ref="A2:H3" xr:uid="{7868C214-BFDF-4A25-882F-CAE0EB840B88}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{CC9EADE2-C5C7-49EF-B259-6BC8BC211BC9}" name="ID" dataDxfId="177"/>
-    <tableColumn id="2" xr3:uid="{AC17126E-DD66-4ACB-B1E7-B02A7079B965}" name="Nombre de Entregable" dataDxfId="176"/>
-    <tableColumn id="3" xr3:uid="{18363FD0-890A-482D-97F4-EB7F38691023}" name="Nombre de Actividad" dataDxfId="175"/>
-    <tableColumn id="4" xr3:uid="{C72FF07B-2371-4C20-BE36-807AC4AB6F52}" name="Fecha de actualización" dataDxfId="174"/>
-    <tableColumn id="5" xr3:uid="{BC64BC7A-2F6A-4299-8F7E-46353544393B}" name="Responsable" dataDxfId="173"/>
-    <tableColumn id="6" xr3:uid="{7945D032-93FB-4F26-8474-2F0B55FD481D}" name="Fecha inicio" dataDxfId="172"/>
-    <tableColumn id="7" xr3:uid="{932845CD-84C0-4B93-A0D7-BB031AC482A8}" name="Fecha de entrega" dataDxfId="171"/>
-    <tableColumn id="8" xr3:uid="{0EFA37AD-6861-45C1-853A-6D922F1671E5}" name="Estatus" dataDxfId="170"/>
+    <tableColumn id="1" xr3:uid="{CC9EADE2-C5C7-49EF-B259-6BC8BC211BC9}" name="ID" dataDxfId="166"/>
+    <tableColumn id="2" xr3:uid="{AC17126E-DD66-4ACB-B1E7-B02A7079B965}" name="Nombre de Entregable" dataDxfId="165"/>
+    <tableColumn id="3" xr3:uid="{18363FD0-890A-482D-97F4-EB7F38691023}" name="Nombre de Actividad" dataDxfId="164"/>
+    <tableColumn id="4" xr3:uid="{C72FF07B-2371-4C20-BE36-807AC4AB6F52}" name="Fecha de actualización" dataDxfId="163"/>
+    <tableColumn id="5" xr3:uid="{BC64BC7A-2F6A-4299-8F7E-46353544393B}" name="Responsable" dataDxfId="162"/>
+    <tableColumn id="6" xr3:uid="{7945D032-93FB-4F26-8474-2F0B55FD481D}" name="Fecha inicio" dataDxfId="161"/>
+    <tableColumn id="7" xr3:uid="{932845CD-84C0-4B93-A0D7-BB031AC482A8}" name="Fecha de entrega" dataDxfId="160"/>
+    <tableColumn id="8" xr3:uid="{0EFA37AD-6861-45C1-853A-6D922F1671E5}" name="Estatus" dataDxfId="159"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C6419CB9-D693-4C43-AB6B-0108540848BF}" name="Tabla12" displayName="Tabla12" ref="A2:H3" totalsRowShown="0" headerRowDxfId="72" headerRowBorderDxfId="81" tableBorderDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C6419CB9-D693-4C43-AB6B-0108540848BF}" name="Tabla12" displayName="Tabla12" ref="A2:H3" totalsRowShown="0" headerRowDxfId="73" headerRowBorderDxfId="72" tableBorderDxfId="71">
   <autoFilter ref="A2:H3" xr:uid="{C6419CB9-D693-4C43-AB6B-0108540848BF}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E1B88EAB-403D-42E4-907C-888A7FEAA0AB}" name="ID" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{62C6D549-55CB-4062-9F68-6D433D6E62D4}" name="Nombre de Entregable" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{F8698F45-D99E-4294-863C-32CC909CA2C7}" name="Nombre de Actividad" dataDxfId="78"/>
-    <tableColumn id="4" xr3:uid="{053C7509-C489-44EC-A86A-5540F0885190}" name="Fecha de actualización" dataDxfId="77"/>
-    <tableColumn id="5" xr3:uid="{284FF323-9B0A-4AEE-90F2-91CECCA4E189}" name="Responsable" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{2F9F9870-4F13-42EB-B14C-538DD103AF5C}" name="Fecha inicio" dataDxfId="75"/>
-    <tableColumn id="7" xr3:uid="{03C5F4F3-B5B6-4B43-9A6C-7EC630ACD61E}" name="Fecha de entrega" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{5848023C-8403-4D79-9FE3-26FC8750D3FF}" name="Estatus" dataDxfId="73"/>
+    <tableColumn id="1" xr3:uid="{E1B88EAB-403D-42E4-907C-888A7FEAA0AB}" name="ID" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{62C6D549-55CB-4062-9F68-6D433D6E62D4}" name="Nombre de Entregable" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{F8698F45-D99E-4294-863C-32CC909CA2C7}" name="Nombre de Actividad" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{053C7509-C489-44EC-A86A-5540F0885190}" name="Fecha de actualización" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{284FF323-9B0A-4AEE-90F2-91CECCA4E189}" name="Responsable" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{2F9F9870-4F13-42EB-B14C-538DD103AF5C}" name="Fecha inicio" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{03C5F4F3-B5B6-4B43-9A6C-7EC630ACD61E}" name="Fecha de entrega" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{5848023C-8403-4D79-9FE3-26FC8750D3FF}" name="Estatus" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{091A29F8-6F53-4C60-B933-1B69228E2F9F}" name="Tabla13" displayName="Tabla13" ref="A2:H3" totalsRowShown="0" headerRowDxfId="60" headerRowBorderDxfId="70" tableBorderDxfId="71" totalsRowBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{091A29F8-6F53-4C60-B933-1B69228E2F9F}" name="Tabla13" displayName="Tabla13" ref="A2:H3" totalsRowShown="0" headerRowDxfId="63" headerRowBorderDxfId="62" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <autoFilter ref="A2:H3" xr:uid="{091A29F8-6F53-4C60-B933-1B69228E2F9F}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1A894A00-9882-4A79-957A-9F55026AFC5B}" name="ID" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{3DE1F71D-8877-4B0B-B12B-939F68C96EB7}" name="Nombre de Entregable" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{8EBAF42E-6E51-4F5B-84A6-8BFBCDBAF37C}" name="Nombre de Actividad" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{830C8CFB-C46A-47F7-9E12-69F9CC5B2E8D}" name="Fecha de actualización" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{154C93F5-FAD8-42D1-9EC5-A9DEF164C2A1}" name="Responsable" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{38433C46-2E86-4654-A38E-91BF6CAC8932}" name="Fecha inicio" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{DF7C84DD-0E59-47D3-B0A5-D8D34BB2629D}" name="Fecha de entrega" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{ECB38F59-22B9-4A9C-831B-146807295842}" name="Estatus" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{1A894A00-9882-4A79-957A-9F55026AFC5B}" name="ID" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{3DE1F71D-8877-4B0B-B12B-939F68C96EB7}" name="Nombre de Entregable" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{8EBAF42E-6E51-4F5B-84A6-8BFBCDBAF37C}" name="Nombre de Actividad" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{830C8CFB-C46A-47F7-9E12-69F9CC5B2E8D}" name="Fecha de actualización" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{154C93F5-FAD8-42D1-9EC5-A9DEF164C2A1}" name="Responsable" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{38433C46-2E86-4654-A38E-91BF6CAC8932}" name="Fecha inicio" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{DF7C84DD-0E59-47D3-B0A5-D8D34BB2629D}" name="Fecha de entrega" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{ECB38F59-22B9-4A9C-831B-146807295842}" name="Estatus" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{95CD6BE5-0A74-4651-8CB8-F4059B6D914D}" name="Tabla14" displayName="Tabla14" ref="A2:H3" totalsRowShown="0" headerRowDxfId="48" headerRowBorderDxfId="58" tableBorderDxfId="59" totalsRowBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{95CD6BE5-0A74-4651-8CB8-F4059B6D914D}" name="Tabla14" displayName="Tabla14" ref="A2:H3" totalsRowShown="0" headerRowDxfId="52" headerRowBorderDxfId="51" tableBorderDxfId="50" totalsRowBorderDxfId="49">
   <autoFilter ref="A2:H3" xr:uid="{95CD6BE5-0A74-4651-8CB8-F4059B6D914D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{BAA4D162-F153-4D04-B8A5-829645D6BEB1}" name="ID" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{3DC2CF2C-1259-4A94-A3BA-6B6492630881}" name="Nombre de Entregable" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{0009076D-F448-4E25-AA64-55BFDA30801A}" name="Nombre de Actividad" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{7610B40B-DB81-4799-829E-1F3F3393B942}" name="Fecha de actualización" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{1BF15C9E-81FF-4E1E-8C63-62A1200DE4B3}" name="Responsable" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{5A974988-AC5E-41E5-936D-677D58059624}" name="Fecha inicio" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{DFF7E2C3-6E9A-49FF-8DED-5D177074BE80}" name="Fecha de entrega" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{1AD7B2CE-EE92-48D7-9E6C-8D0D2A7AE698}" name="Estatus" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{BAA4D162-F153-4D04-B8A5-829645D6BEB1}" name="ID" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{3DC2CF2C-1259-4A94-A3BA-6B6492630881}" name="Nombre de Entregable" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{0009076D-F448-4E25-AA64-55BFDA30801A}" name="Nombre de Actividad" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{7610B40B-DB81-4799-829E-1F3F3393B942}" name="Fecha de actualización" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{1BF15C9E-81FF-4E1E-8C63-62A1200DE4B3}" name="Responsable" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{5A974988-AC5E-41E5-936D-677D58059624}" name="Fecha inicio" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{DFF7E2C3-6E9A-49FF-8DED-5D177074BE80}" name="Fecha de entrega" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{1AD7B2CE-EE92-48D7-9E6C-8D0D2A7AE698}" name="Estatus" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{C09023BD-0067-477B-A125-892356321158}" name="Tabla15" displayName="Tabla15" ref="A1:H2" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="46" tableBorderDxfId="47" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{C09023BD-0067-477B-A125-892356321158}" name="Tabla15" displayName="Tabla15" ref="A1:H2" totalsRowShown="0" headerRowDxfId="42" headerRowBorderDxfId="41" tableBorderDxfId="40" totalsRowBorderDxfId="39">
   <autoFilter ref="A1:H2" xr:uid="{C09023BD-0067-477B-A125-892356321158}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{5C7AB9DE-91B5-4FB0-896F-DBAEF7A7D73E}" name="ID" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{186C4FB2-90F7-404A-9D84-EEEC230C2B78}" name="Nombre de Entregable" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{460FE5C8-31C0-460A-97F8-FA2761F67558}" name="Nombre de Actividad" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{39F0CCF3-5A7C-4B85-B125-9B3F5412728C}" name="Fecha de actualización" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{BF1BDD6F-A62B-4066-A27A-2D5F24B56345}" name="Responsable" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{4764D51F-D455-4A5E-8354-6DCAD460B729}" name="Fecha inicio" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{F8EC2F1B-8F50-46F1-9B9F-C7ED30B3C4A8}" name="Fecha de entrega" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{64CFE3A7-FD57-41C6-A3F0-FB7EF80E0573}" name="Estatus" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{5C7AB9DE-91B5-4FB0-896F-DBAEF7A7D73E}" name="ID" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{186C4FB2-90F7-404A-9D84-EEEC230C2B78}" name="Nombre de Entregable" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{460FE5C8-31C0-460A-97F8-FA2761F67558}" name="Nombre de Actividad" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{39F0CCF3-5A7C-4B85-B125-9B3F5412728C}" name="Fecha de actualización" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{BF1BDD6F-A62B-4066-A27A-2D5F24B56345}" name="Responsable" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{4764D51F-D455-4A5E-8354-6DCAD460B729}" name="Fecha inicio" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{F8EC2F1B-8F50-46F1-9B9F-C7ED30B3C4A8}" name="Fecha de entrega" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{64CFE3A7-FD57-41C6-A3F0-FB7EF80E0573}" name="Estatus" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{26ECABAE-D33E-44AB-B016-93DAC3C46C83}" name="Tabla16" displayName="Tabla16" ref="A2:H3" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="34" tableBorderDxfId="35" totalsRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{26ECABAE-D33E-44AB-B016-93DAC3C46C83}" name="Tabla16" displayName="Tabla16" ref="A2:H3" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A2:H3" xr:uid="{26ECABAE-D33E-44AB-B016-93DAC3C46C83}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{692C21BE-7C9E-45E5-8194-4538C6397728}" name="ID" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{40A16DB2-90EF-4CDB-84DE-A718750C5703}" name="Nombre de Entregable" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{AFC81BF1-FC84-416F-A1F3-3DCB21707A8C}" name="Nombre de Actividad" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{D09AB75B-DA77-4B59-BF7C-98B57BDF2D23}" name="Fecha de actualización" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{EC2659AB-2F09-473F-A184-E50BBC778B7C}" name="Responsable" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{FC617FD9-865A-4B4C-8FF7-B68AC3977930}" name="Fecha inicio" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{1948E123-CDE6-4A51-8091-678AF8125A3A}" name="Fecha de entrega" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{B95B1329-EBAF-41A8-A04A-9E8C10E530EF}" name="Estatus" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{692C21BE-7C9E-45E5-8194-4538C6397728}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{40A16DB2-90EF-4CDB-84DE-A718750C5703}" name="Nombre de Entregable" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{AFC81BF1-FC84-416F-A1F3-3DCB21707A8C}" name="Nombre de Actividad" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{D09AB75B-DA77-4B59-BF7C-98B57BDF2D23}" name="Fecha de actualización" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{EC2659AB-2F09-473F-A184-E50BBC778B7C}" name="Responsable" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{FC617FD9-865A-4B4C-8FF7-B68AC3977930}" name="Fecha inicio" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{1948E123-CDE6-4A51-8091-678AF8125A3A}" name="Fecha de entrega" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{B95B1329-EBAF-41A8-A04A-9E8C10E530EF}" name="Estatus" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{141EFD2D-8484-4477-B4BB-82973B6098A9}" name="Tabla17" displayName="Tabla17" ref="A2:H3" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{141EFD2D-8484-4477-B4BB-82973B6098A9}" name="Tabla17" displayName="Tabla17" ref="A2:H3" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <autoFilter ref="A2:H3" xr:uid="{141EFD2D-8484-4477-B4BB-82973B6098A9}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F590E58C-3D45-40E7-9136-AC701CE6D88E}" name="ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{C4BF3588-3312-43E2-9292-C74A033D9560}" name="Nombre de Entregable" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{7D727AF9-B3B0-4413-9FA1-CB8A88F4D4DB}" name="Nombre de Actividad" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{8931FCD5-E90D-4936-A962-9AB0ECC1DE29}" name="Fecha de actualización" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{9D2CFF51-5E90-4486-995A-5624036CCCBD}" name="Responsable" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{C7228B95-6877-4AE9-B6DB-3F2A0F776E6E}" name="Fecha inicio" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{BABE6FE6-55CE-4FA6-A6FB-A3AD42E35BE9}" name="Fecha de entrega" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{F590E58C-3D45-40E7-9136-AC701CE6D88E}" name="ID" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{C4BF3588-3312-43E2-9292-C74A033D9560}" name="Nombre de Entregable" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{7D727AF9-B3B0-4413-9FA1-CB8A88F4D4DB}" name="Nombre de Actividad" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{8931FCD5-E90D-4936-A962-9AB0ECC1DE29}" name="Fecha de actualización" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{9D2CFF51-5E90-4486-995A-5624036CCCBD}" name="Responsable" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{C7228B95-6877-4AE9-B6DB-3F2A0F776E6E}" name="Fecha inicio" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{BABE6FE6-55CE-4FA6-A6FB-A3AD42E35BE9}" name="Fecha de entrega" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{3993C7C5-5CE1-4D8F-8DF1-388BF9B56179}" name="Estatus" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4849,143 +4847,143 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{53BED175-6551-41E7-8138-05B651F11323}" name="Tabla18" displayName="Tabla18" ref="A2:H3" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{53BED175-6551-41E7-8138-05B651F11323}" name="Tabla18" displayName="Tabla18" ref="A2:H3" totalsRowShown="0" headerRowDxfId="180" headerRowBorderDxfId="179" tableBorderDxfId="178" totalsRowBorderDxfId="177">
   <autoFilter ref="A2:H3" xr:uid="{53BED175-6551-41E7-8138-05B651F11323}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1F36D69C-DE8D-4F9D-964F-983B4FAA9751}" name="ID" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{82E8B485-F269-41B4-AEF4-187AF2A555A2}" name="Nombre de Entregable" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{B58BBB46-55C8-4ED2-87C4-678C046B326E}" name="Nombre de Actividad" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{C8F87775-AD70-4E54-A8A1-AF19F077730B}" name="Fecha de actualización" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{BDC15FEE-B36E-42B3-BAD5-A2B28A28B6F9}" name="Responsable" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{D10576F3-F238-46E2-957B-D1D3B837DED8}" name="Fecha inicio" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{C36D7B50-9C2C-4EF3-9886-EDD889CDD238}" name="Fecha de entrega" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{2B4F83C3-439C-4C58-B615-AE798BA87693}" name="Estatus" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{1F36D69C-DE8D-4F9D-964F-983B4FAA9751}" name="ID" dataDxfId="176"/>
+    <tableColumn id="2" xr3:uid="{82E8B485-F269-41B4-AEF4-187AF2A555A2}" name="Nombre de Entregable" dataDxfId="175"/>
+    <tableColumn id="3" xr3:uid="{B58BBB46-55C8-4ED2-87C4-678C046B326E}" name="Nombre de Actividad" dataDxfId="174"/>
+    <tableColumn id="4" xr3:uid="{C8F87775-AD70-4E54-A8A1-AF19F077730B}" name="Fecha de actualización" dataDxfId="173"/>
+    <tableColumn id="5" xr3:uid="{BDC15FEE-B36E-42B3-BAD5-A2B28A28B6F9}" name="Responsable" dataDxfId="172"/>
+    <tableColumn id="6" xr3:uid="{D10576F3-F238-46E2-957B-D1D3B837DED8}" name="Fecha inicio" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{C36D7B50-9C2C-4EF3-9886-EDD889CDD238}" name="Fecha de entrega" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{2B4F83C3-439C-4C58-B615-AE798BA87693}" name="Estatus" dataDxfId="171"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{691F3764-10DC-463F-9E30-9CF4A35DD9DA}" name="Tabla4" displayName="Tabla4" ref="A2:H3" totalsRowShown="0" headerRowDxfId="158" headerRowBorderDxfId="167" tableBorderDxfId="168">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{691F3764-10DC-463F-9E30-9CF4A35DD9DA}" name="Tabla4" displayName="Tabla4" ref="A2:H3" totalsRowShown="0" headerRowDxfId="158" headerRowBorderDxfId="157" tableBorderDxfId="156">
   <autoFilter ref="A2:H3" xr:uid="{691F3764-10DC-463F-9E30-9CF4A35DD9DA}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{B97B5307-5339-4A0C-9B38-A7D08811685B}" name="ID" dataDxfId="166"/>
-    <tableColumn id="2" xr3:uid="{20D90F8D-AAF4-4C2A-A114-9403108A1CC1}" name="Nombre de Entregable" dataDxfId="165"/>
-    <tableColumn id="3" xr3:uid="{00F7DE12-7A94-4433-8144-B3F573DA9C72}" name="Nombre de Actividad" dataDxfId="164"/>
-    <tableColumn id="4" xr3:uid="{BD2A84A1-42BD-4A56-A325-A382100714AB}" name="Fecha de actualización" dataDxfId="163"/>
-    <tableColumn id="5" xr3:uid="{7405CACB-ADC2-4DCE-A630-A6E105D37242}" name="Responsable" dataDxfId="162"/>
-    <tableColumn id="6" xr3:uid="{94CC9F95-4C5A-4357-97B7-61EBF37B1FD6}" name="Fecha inicio" dataDxfId="161"/>
-    <tableColumn id="7" xr3:uid="{572FD4E5-E1CE-432E-8F42-EF0398EDA7E6}" name="Fecha de entrega" dataDxfId="160"/>
-    <tableColumn id="8" xr3:uid="{B351B91E-CB4D-4C1E-9743-E8694E4AFE6F}" name="Estatus" dataDxfId="159"/>
+    <tableColumn id="1" xr3:uid="{B97B5307-5339-4A0C-9B38-A7D08811685B}" name="ID" dataDxfId="155"/>
+    <tableColumn id="2" xr3:uid="{20D90F8D-AAF4-4C2A-A114-9403108A1CC1}" name="Nombre de Entregable" dataDxfId="154"/>
+    <tableColumn id="3" xr3:uid="{00F7DE12-7A94-4433-8144-B3F573DA9C72}" name="Nombre de Actividad" dataDxfId="153"/>
+    <tableColumn id="4" xr3:uid="{BD2A84A1-42BD-4A56-A325-A382100714AB}" name="Fecha de actualización" dataDxfId="152"/>
+    <tableColumn id="5" xr3:uid="{7405CACB-ADC2-4DCE-A630-A6E105D37242}" name="Responsable" dataDxfId="151"/>
+    <tableColumn id="6" xr3:uid="{94CC9F95-4C5A-4357-97B7-61EBF37B1FD6}" name="Fecha inicio" dataDxfId="150"/>
+    <tableColumn id="7" xr3:uid="{572FD4E5-E1CE-432E-8F42-EF0398EDA7E6}" name="Fecha de entrega" dataDxfId="149"/>
+    <tableColumn id="8" xr3:uid="{B351B91E-CB4D-4C1E-9743-E8694E4AFE6F}" name="Estatus" dataDxfId="148"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{41D906CD-E4F5-4727-8777-9B10F530B31D}" name="Tabla5" displayName="Tabla5" ref="A2:H3" totalsRowShown="0" headerRowDxfId="147" headerRowBorderDxfId="156" tableBorderDxfId="157">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{41D906CD-E4F5-4727-8777-9B10F530B31D}" name="Tabla5" displayName="Tabla5" ref="A2:H3" totalsRowShown="0" headerRowDxfId="147" headerRowBorderDxfId="146" tableBorderDxfId="145">
   <autoFilter ref="A2:H3" xr:uid="{41D906CD-E4F5-4727-8777-9B10F530B31D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{15EB7597-7B47-4563-B28C-B7C337540CCD}" name="ID" dataDxfId="155"/>
-    <tableColumn id="2" xr3:uid="{43821FEA-E112-4A0E-AB69-F8D42416BEA7}" name="Nombre de Entregable" dataDxfId="154"/>
-    <tableColumn id="3" xr3:uid="{822D0D8B-D71F-4B16-AD1B-91AA51E8BB15}" name="Nombre de Actividad" dataDxfId="153"/>
-    <tableColumn id="4" xr3:uid="{D5172D8B-4766-4078-8168-4D6AECB8EA1D}" name="Fecha de actualización" dataDxfId="152"/>
-    <tableColumn id="5" xr3:uid="{D3AC480C-B83D-4558-92E3-59E3E66065D0}" name="Responsable" dataDxfId="151"/>
-    <tableColumn id="6" xr3:uid="{9FF5F994-CD6E-4A1E-AD37-B8413F735AE4}" name="Fecha inicio" dataDxfId="150"/>
-    <tableColumn id="7" xr3:uid="{859705EF-2E6B-4F4E-B0D6-9D653553D028}" name="Fecha de entrega" dataDxfId="149"/>
-    <tableColumn id="8" xr3:uid="{DC45E00E-E203-4857-84AF-4FE970D165F1}" name="Estatus" dataDxfId="148"/>
+    <tableColumn id="1" xr3:uid="{15EB7597-7B47-4563-B28C-B7C337540CCD}" name="ID" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{43821FEA-E112-4A0E-AB69-F8D42416BEA7}" name="Nombre de Entregable" dataDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{822D0D8B-D71F-4B16-AD1B-91AA51E8BB15}" name="Nombre de Actividad" dataDxfId="142"/>
+    <tableColumn id="4" xr3:uid="{D5172D8B-4766-4078-8168-4D6AECB8EA1D}" name="Fecha de actualización" dataDxfId="141"/>
+    <tableColumn id="5" xr3:uid="{D3AC480C-B83D-4558-92E3-59E3E66065D0}" name="Responsable" dataDxfId="140"/>
+    <tableColumn id="6" xr3:uid="{9FF5F994-CD6E-4A1E-AD37-B8413F735AE4}" name="Fecha inicio" dataDxfId="139"/>
+    <tableColumn id="7" xr3:uid="{859705EF-2E6B-4F4E-B0D6-9D653553D028}" name="Fecha de entrega" dataDxfId="138"/>
+    <tableColumn id="8" xr3:uid="{DC45E00E-E203-4857-84AF-4FE970D165F1}" name="Estatus" dataDxfId="137"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B7EADDC3-63D4-402A-81A8-2D9F1F4F4928}" name="Tabla6" displayName="Tabla6" ref="A1:H2" totalsRowShown="0" headerRowDxfId="135" headerRowBorderDxfId="145" tableBorderDxfId="146" totalsRowBorderDxfId="144">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B7EADDC3-63D4-402A-81A8-2D9F1F4F4928}" name="Tabla6" displayName="Tabla6" ref="A1:H2" totalsRowShown="0" headerRowDxfId="136" headerRowBorderDxfId="135" tableBorderDxfId="134" totalsRowBorderDxfId="133">
   <autoFilter ref="A1:H2" xr:uid="{B7EADDC3-63D4-402A-81A8-2D9F1F4F4928}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1A6D13DD-E874-43AE-9285-C28F9A02B215}" name="ID" dataDxfId="143"/>
-    <tableColumn id="2" xr3:uid="{E1BEC8D9-158D-42D9-BD79-D0B82135DF79}" name="Nombre de Entregable" dataDxfId="142"/>
-    <tableColumn id="3" xr3:uid="{CC6C20AA-744D-44AB-98D6-F3579CB650C2}" name="Nombre de Actividad" dataDxfId="141"/>
-    <tableColumn id="4" xr3:uid="{5E592363-D8B2-4ADF-9703-C1F44A366AA8}" name="Fecha de actualización" dataDxfId="140"/>
-    <tableColumn id="5" xr3:uid="{3691854D-A926-43FF-A057-E148A4E86B66}" name="Responsable" dataDxfId="139"/>
-    <tableColumn id="6" xr3:uid="{E6B01348-C9D1-45AC-A8AF-27B0E04E6D00}" name="Fecha inicio" dataDxfId="138"/>
-    <tableColumn id="7" xr3:uid="{977E082C-1194-4972-9F3B-8701A8867AFF}" name="Fecha de entrega" dataDxfId="137"/>
-    <tableColumn id="8" xr3:uid="{26D3D519-FA9F-495D-8319-0BB89F375F5A}" name="Estatus" dataDxfId="136"/>
+    <tableColumn id="1" xr3:uid="{1A6D13DD-E874-43AE-9285-C28F9A02B215}" name="ID" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{E1BEC8D9-158D-42D9-BD79-D0B82135DF79}" name="Nombre de Entregable" dataDxfId="131"/>
+    <tableColumn id="3" xr3:uid="{CC6C20AA-744D-44AB-98D6-F3579CB650C2}" name="Nombre de Actividad" dataDxfId="130"/>
+    <tableColumn id="4" xr3:uid="{5E592363-D8B2-4ADF-9703-C1F44A366AA8}" name="Fecha de actualización" dataDxfId="129"/>
+    <tableColumn id="5" xr3:uid="{3691854D-A926-43FF-A057-E148A4E86B66}" name="Responsable" dataDxfId="128"/>
+    <tableColumn id="6" xr3:uid="{E6B01348-C9D1-45AC-A8AF-27B0E04E6D00}" name="Fecha inicio" dataDxfId="127"/>
+    <tableColumn id="7" xr3:uid="{977E082C-1194-4972-9F3B-8701A8867AFF}" name="Fecha de entrega" dataDxfId="126"/>
+    <tableColumn id="8" xr3:uid="{26D3D519-FA9F-495D-8319-0BB89F375F5A}" name="Estatus" dataDxfId="125"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4C842EE6-6106-4CEE-B46E-DE3932BF8492}" name="Tabla7" displayName="Tabla7" ref="A2:H3" totalsRowShown="0" headerRowDxfId="123" headerRowBorderDxfId="133" tableBorderDxfId="134" totalsRowBorderDxfId="132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4C842EE6-6106-4CEE-B46E-DE3932BF8492}" name="Tabla7" displayName="Tabla7" ref="A2:H3" totalsRowShown="0" headerRowDxfId="124" headerRowBorderDxfId="123" tableBorderDxfId="122" totalsRowBorderDxfId="121">
   <autoFilter ref="A2:H3" xr:uid="{4C842EE6-6106-4CEE-B46E-DE3932BF8492}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A5988091-E833-4BA0-ACE6-5F6C896BE27B}" name="ID" dataDxfId="131"/>
-    <tableColumn id="2" xr3:uid="{8528F8EF-B638-4A2F-B06F-F85B3CC89077}" name="Nombre de Entregable" dataDxfId="130"/>
-    <tableColumn id="3" xr3:uid="{855F2AD4-446D-414E-AED8-E50B24580DA6}" name="Nombre de Actividad" dataDxfId="129"/>
-    <tableColumn id="4" xr3:uid="{1CB02499-6774-4F01-8C33-F242078D5D9B}" name="Fecha de actualización" dataDxfId="128"/>
-    <tableColumn id="5" xr3:uid="{AE398FE8-0890-41A3-99EE-6415F0AC009A}" name="Responsable" dataDxfId="127"/>
-    <tableColumn id="6" xr3:uid="{4AA2699F-5D2E-4040-960F-312E70A3A437}" name="Fecha inicio" dataDxfId="126"/>
-    <tableColumn id="7" xr3:uid="{837CD670-82B8-4BDE-9763-DD108FFAF4FB}" name="Fecha de entrega" dataDxfId="125"/>
-    <tableColumn id="8" xr3:uid="{D0BE3AE1-9254-456A-B9F6-C4E0089A71B1}" name="Estatus" dataDxfId="124"/>
+    <tableColumn id="1" xr3:uid="{A5988091-E833-4BA0-ACE6-5F6C896BE27B}" name="ID" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{8528F8EF-B638-4A2F-B06F-F85B3CC89077}" name="Nombre de Entregable" dataDxfId="119"/>
+    <tableColumn id="3" xr3:uid="{855F2AD4-446D-414E-AED8-E50B24580DA6}" name="Nombre de Actividad" dataDxfId="118"/>
+    <tableColumn id="4" xr3:uid="{1CB02499-6774-4F01-8C33-F242078D5D9B}" name="Fecha de actualización" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{AE398FE8-0890-41A3-99EE-6415F0AC009A}" name="Responsable" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{4AA2699F-5D2E-4040-960F-312E70A3A437}" name="Fecha inicio" dataDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{837CD670-82B8-4BDE-9763-DD108FFAF4FB}" name="Fecha de entrega" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{D0BE3AE1-9254-456A-B9F6-C4E0089A71B1}" name="Estatus" dataDxfId="113"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3173728F-4987-4A9D-B486-16D0122F4CB5}" name="Tabla8" displayName="Tabla8" ref="A2:H3" totalsRowShown="0" headerRowDxfId="111" headerRowBorderDxfId="121" tableBorderDxfId="122" totalsRowBorderDxfId="120">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3173728F-4987-4A9D-B486-16D0122F4CB5}" name="Tabla8" displayName="Tabla8" ref="A2:H3" totalsRowShown="0" headerRowDxfId="112" headerRowBorderDxfId="111" tableBorderDxfId="110" totalsRowBorderDxfId="109">
   <autoFilter ref="A2:H3" xr:uid="{3173728F-4987-4A9D-B486-16D0122F4CB5}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{83A036D1-DC97-4CF1-B8AB-765DE1F634B4}" name="ID" dataDxfId="119"/>
-    <tableColumn id="2" xr3:uid="{27753FB0-1F07-4F98-8974-9951C7247B6A}" name="Nombre de Entregable" dataDxfId="118"/>
-    <tableColumn id="3" xr3:uid="{7D33DF5B-4C8B-45CC-A702-2398CC804199}" name="Nombre de Actividad" dataDxfId="117"/>
-    <tableColumn id="4" xr3:uid="{E5B400EF-31E9-4DCA-9017-3E7F6378F89B}" name="Fecha de actualización" dataDxfId="116"/>
-    <tableColumn id="5" xr3:uid="{23CBCED6-47E8-4484-90D9-87757A8E3A34}" name="Responsable" dataDxfId="115"/>
-    <tableColumn id="6" xr3:uid="{254E5A46-1766-412E-A223-150654664F8F}" name="Fecha inicio" dataDxfId="114"/>
-    <tableColumn id="7" xr3:uid="{9C78875D-DF21-4BD8-868F-E54215477301}" name="Fecha de entrega" dataDxfId="113"/>
-    <tableColumn id="8" xr3:uid="{AC70ABDD-FB8B-4B99-A433-B007F4C21026}" name="Estatus" dataDxfId="112"/>
+    <tableColumn id="1" xr3:uid="{83A036D1-DC97-4CF1-B8AB-765DE1F634B4}" name="ID" dataDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{27753FB0-1F07-4F98-8974-9951C7247B6A}" name="Nombre de Entregable" dataDxfId="107"/>
+    <tableColumn id="3" xr3:uid="{7D33DF5B-4C8B-45CC-A702-2398CC804199}" name="Nombre de Actividad" dataDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{E5B400EF-31E9-4DCA-9017-3E7F6378F89B}" name="Fecha de actualización" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{23CBCED6-47E8-4484-90D9-87757A8E3A34}" name="Responsable" dataDxfId="104"/>
+    <tableColumn id="6" xr3:uid="{254E5A46-1766-412E-A223-150654664F8F}" name="Fecha inicio" dataDxfId="103"/>
+    <tableColumn id="7" xr3:uid="{9C78875D-DF21-4BD8-868F-E54215477301}" name="Fecha de entrega" dataDxfId="102"/>
+    <tableColumn id="8" xr3:uid="{AC70ABDD-FB8B-4B99-A433-B007F4C21026}" name="Estatus" dataDxfId="101"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C3093EA8-49BA-4911-ACA3-DA7373204A76}" name="Tabla9" displayName="Tabla9" ref="A2:H3" totalsRowShown="0" headerRowDxfId="99" headerRowBorderDxfId="109" tableBorderDxfId="110" totalsRowBorderDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C3093EA8-49BA-4911-ACA3-DA7373204A76}" name="Tabla9" displayName="Tabla9" ref="A2:H3" totalsRowShown="0" headerRowDxfId="100" headerRowBorderDxfId="99" tableBorderDxfId="98" totalsRowBorderDxfId="97">
   <autoFilter ref="A2:H3" xr:uid="{C3093EA8-49BA-4911-ACA3-DA7373204A76}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AA5CB639-A460-47A8-AB83-38C84DDE3D58}" name="ID" dataDxfId="107"/>
-    <tableColumn id="2" xr3:uid="{3D091B9B-9731-464E-9751-CB4BB1D6259B}" name="Nombre de Entregable" dataDxfId="106"/>
-    <tableColumn id="3" xr3:uid="{603DCA62-57B8-4FB2-90F0-3AA6EA9F9471}" name="Nombre de Actividad" dataDxfId="105"/>
-    <tableColumn id="4" xr3:uid="{FAA1C815-14C1-4B22-930F-FC18CF073568}" name="Fecha de actualización" dataDxfId="104"/>
-    <tableColumn id="5" xr3:uid="{721208FF-94EE-45DD-B3D2-F61BFE035467}" name="Responsable" dataDxfId="103"/>
-    <tableColumn id="6" xr3:uid="{4B805201-C2B2-42D8-92F0-0069EFF25EDC}" name="Fecha inicio" dataDxfId="102"/>
-    <tableColumn id="7" xr3:uid="{6ABD43F6-A4F5-40AD-A4D1-FC41FF12B788}" name="Fecha de entrega" dataDxfId="101"/>
-    <tableColumn id="8" xr3:uid="{5FD15412-6689-4237-BDB8-BB427193AEC2}" name="Estatus" dataDxfId="100"/>
+    <tableColumn id="1" xr3:uid="{AA5CB639-A460-47A8-AB83-38C84DDE3D58}" name="ID" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{3D091B9B-9731-464E-9751-CB4BB1D6259B}" name="Nombre de Entregable" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{603DCA62-57B8-4FB2-90F0-3AA6EA9F9471}" name="Nombre de Actividad" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{FAA1C815-14C1-4B22-930F-FC18CF073568}" name="Fecha de actualización" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{721208FF-94EE-45DD-B3D2-F61BFE035467}" name="Responsable" dataDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{4B805201-C2B2-42D8-92F0-0069EFF25EDC}" name="Fecha inicio" dataDxfId="91"/>
+    <tableColumn id="7" xr3:uid="{6ABD43F6-A4F5-40AD-A4D1-FC41FF12B788}" name="Fecha de entrega" dataDxfId="90"/>
+    <tableColumn id="8" xr3:uid="{5FD15412-6689-4237-BDB8-BB427193AEC2}" name="Estatus" dataDxfId="89"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E0F2D28F-AF2B-46E0-81A7-7988676245AB}" name="Tabla10" displayName="Tabla10" ref="A2:H3" totalsRowShown="0" headerRowDxfId="87" headerRowBorderDxfId="97" tableBorderDxfId="98" totalsRowBorderDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E0F2D28F-AF2B-46E0-81A7-7988676245AB}" name="Tabla10" displayName="Tabla10" ref="A2:H3" totalsRowShown="0" headerRowDxfId="88" headerRowBorderDxfId="87" tableBorderDxfId="86" totalsRowBorderDxfId="85">
   <autoFilter ref="A2:H3" xr:uid="{E0F2D28F-AF2B-46E0-81A7-7988676245AB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E0C79D11-E997-4EC1-A1A7-439242F53D34}" name="ID" dataDxfId="95"/>
-    <tableColumn id="2" xr3:uid="{DAF200BB-0E87-4EC9-8C0E-D8E0D6235841}" name="Nombre de Entregable" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{1E489D18-49D9-4D44-B5C9-F3851EC5DDBF}" name="Nombre de Actividad" dataDxfId="93"/>
-    <tableColumn id="4" xr3:uid="{8455378D-8539-4FD0-8E49-EF6FDDBE6717}" name="Fecha de actualización" dataDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{324E51BC-16AD-45F9-AF1D-B306301950C7}" name="Responsable" dataDxfId="91"/>
-    <tableColumn id="6" xr3:uid="{BC2E24B6-0C7F-45B9-AE17-B3FC93288580}" name="Fecha inicio" dataDxfId="90"/>
-    <tableColumn id="7" xr3:uid="{4CB7B3B1-D79A-412B-A916-6E987A8BA95A}" name="Fecha de entrega" dataDxfId="89"/>
-    <tableColumn id="8" xr3:uid="{DE74C01E-44C0-4CED-A9A0-2E20134D2DF2}" name="Estatus" dataDxfId="88"/>
+    <tableColumn id="1" xr3:uid="{E0C79D11-E997-4EC1-A1A7-439242F53D34}" name="ID" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{DAF200BB-0E87-4EC9-8C0E-D8E0D6235841}" name="Nombre de Entregable" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{1E489D18-49D9-4D44-B5C9-F3851EC5DDBF}" name="Nombre de Actividad" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{8455378D-8539-4FD0-8E49-EF6FDDBE6717}" name="Fecha de actualización" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{324E51BC-16AD-45F9-AF1D-B306301950C7}" name="Responsable" dataDxfId="80"/>
+    <tableColumn id="6" xr3:uid="{BC2E24B6-0C7F-45B9-AE17-B3FC93288580}" name="Fecha inicio" dataDxfId="79"/>
+    <tableColumn id="7" xr3:uid="{4CB7B3B1-D79A-412B-A916-6E987A8BA95A}" name="Fecha de entrega" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{DE74C01E-44C0-4CED-A9A0-2E20134D2DF2}" name="Estatus" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4C23B88C-478A-4D9E-A87D-064399D524BE}" name="Tabla11" displayName="Tabla11" ref="A2:I4" totalsRowShown="0" headerRowDxfId="83" headerRowBorderDxfId="85" tableBorderDxfId="86" totalsRowBorderDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4C23B88C-478A-4D9E-A87D-064399D524BE}" name="Tabla11" displayName="Tabla11" ref="A2:I4" totalsRowShown="0" headerRowDxfId="77" headerRowBorderDxfId="76" tableBorderDxfId="75" totalsRowBorderDxfId="74">
   <autoFilter ref="A2:I4" xr:uid="{4C23B88C-478A-4D9E-A87D-064399D524BE}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{8E6CC921-4CFE-48CA-AF4D-89ECEC03F55D}" name="Columna1"/>
@@ -5332,54 +5330,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46086</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="18">
         <v>46072</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="18">
         <v>46086</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="20" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5387,137 +5385,137 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -5562,34 +5560,34 @@
     <col min="8" max="8" width="58.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="21" t="s">
         <v>124</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5607,10 +5605,10 @@
       <c r="F3" s="4">
         <v>46090</v>
       </c>
-      <c r="G3" s="4">
-        <v>46100</v>
-      </c>
-      <c r="H3" s="29" t="s">
+      <c r="G3" s="18">
+        <v>46107</v>
+      </c>
+      <c r="H3" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5618,149 +5616,149 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="12"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -5772,17 +5770,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B16:H16"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B16:H16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -5806,55 +5804,55 @@
     <col min="8" max="8" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46088</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="18">
         <v>46090</v>
       </c>
-      <c r="G3" s="35">
-        <v>46100</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="G3" s="18">
+        <v>46107</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5862,135 +5860,135 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -6035,55 +6033,55 @@
     <col min="8" max="8" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46094</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="35">
-        <v>46100</v>
-      </c>
-      <c r="G3" s="35">
-        <v>46105</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="F3" s="18">
+        <v>46108</v>
+      </c>
+      <c r="G3" s="18">
+        <v>46112</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6091,185 +6089,185 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="23"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
-      <c r="B14" s="9" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="25" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="26"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -6281,11 +6279,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B14:H14"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="B7:H7"/>
@@ -6295,6 +6288,11 @@
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B14:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6318,55 +6316,55 @@
     <col min="8" max="8" width="46.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="18">
         <v>46088</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="F2" s="35">
-        <v>46100</v>
-      </c>
-      <c r="G2" s="35">
-        <v>46105</v>
-      </c>
-      <c r="H2" s="37" t="s">
+      <c r="F2" s="18">
+        <v>46108</v>
+      </c>
+      <c r="G2" s="18">
+        <v>46112</v>
+      </c>
+      <c r="H2" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6374,137 +6372,137 @@
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -6549,55 +6547,55 @@
     <col min="8" max="8" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46088</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="F3" s="35">
-        <v>46105</v>
-      </c>
-      <c r="G3" s="35">
-        <v>46107</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="F3" s="18">
+        <v>46112</v>
+      </c>
+      <c r="G3" s="18">
+        <v>46112</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6605,137 +6603,137 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -6779,55 +6777,55 @@
     <col min="8" max="8" width="27.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46088</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="F3" s="35">
-        <v>46107</v>
-      </c>
-      <c r="G3" s="35">
-        <v>46114</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="F3" s="18">
+        <v>46112</v>
+      </c>
+      <c r="G3" s="18">
+        <v>46122</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6835,137 +6833,137 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -7010,55 +7008,55 @@
     <col min="8" max="8" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46088</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="F3" s="35">
-        <v>46114</v>
-      </c>
-      <c r="G3" s="35">
+      <c r="F3" s="18">
+        <v>46122</v>
+      </c>
+      <c r="G3" s="18">
         <v>46128</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7066,135 +7064,135 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -7240,33 +7238,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7287,7 +7285,7 @@
       <c r="G3" s="4">
         <v>46086</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="12" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7295,137 +7293,137 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="16"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -7472,33 +7470,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="21" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7519,7 +7517,7 @@
       <c r="G3" s="4">
         <v>46086</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="12" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7527,137 +7525,137 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -7702,55 +7700,55 @@
     <col min="7" max="7" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="18">
         <v>46086</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="18">
         <v>46084</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="18">
         <v>46086</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="20" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7758,149 +7756,149 @@
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -7946,55 +7944,55 @@
     <col min="8" max="8" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46086</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="18">
         <v>46084</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="18">
         <v>46086</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="20" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8002,135 +8000,135 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -8177,54 +8175,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46088</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="18">
         <v>46087</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="18">
         <v>46090</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="20" t="s">
         <v>12</v>
       </c>
     </row>
@@ -8232,137 +8230,137 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -8408,55 +8406,55 @@
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46088</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="18">
         <v>46090</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="18">
         <v>46093</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8464,161 +8462,161 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="12"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="12"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F20" t="s">
@@ -8632,18 +8630,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8668,55 +8666,55 @@
     <col min="8" max="8" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="18">
         <v>46088</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="18">
         <v>46090</v>
       </c>
-      <c r="G3" s="35">
-        <v>46100</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="G3" s="18">
+        <v>46107</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8724,135 +8722,135 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -8896,36 +8894,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="15" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -8947,34 +8945,34 @@
       <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="18">
         <v>46088</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="F4" s="36"/>
-      <c r="G4" s="35">
+      <c r="F4" s="19"/>
+      <c r="G4" s="18">
         <v>46090</v>
       </c>
-      <c r="H4" s="35">
-        <v>46100</v>
-      </c>
-      <c r="I4" s="37" t="s">
+      <c r="H4" s="18">
+        <v>46107</v>
+      </c>
+      <c r="I4" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8982,147 +8980,147 @@
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
